--- a/Climatic_Winter_problème.xlsx
+++ b/Climatic_Winter_problème.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN.RDS-PRET-0218\Desktop\Agrocampus Ouest\M2\Projet ingénieur\meteo_vs_rendement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2D5EB55-B78D-4E35-AA05-0F73AC42A1E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48476BF4-ADB6-48F8-92C2-3378561A0B6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -521,8 +521,12 @@
       <c r="A6" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
+      <c r="B6" s="1">
+        <v>41281</v>
+      </c>
+      <c r="C6" s="1">
+        <v>41339</v>
+      </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
     </row>
@@ -530,8 +534,12 @@
       <c r="A7" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
+      <c r="B7" s="1">
+        <v>41594</v>
+      </c>
+      <c r="C7" s="1">
+        <v>41642</v>
+      </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
     </row>
@@ -539,8 +547,12 @@
       <c r="A8" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
+      <c r="B8" s="1">
+        <v>41594</v>
+      </c>
+      <c r="C8" s="1">
+        <v>41625</v>
+      </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
     </row>
@@ -548,8 +560,12 @@
       <c r="A9" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
+      <c r="B9" s="1">
+        <v>41594</v>
+      </c>
+      <c r="C9" s="1">
+        <v>41631</v>
+      </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
     </row>
@@ -557,8 +573,12 @@
       <c r="A10" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
+      <c r="B10" s="1">
+        <v>41598</v>
+      </c>
+      <c r="C10" s="1">
+        <v>41622</v>
+      </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
     </row>
@@ -566,8 +586,12 @@
       <c r="A11" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
+      <c r="B11" s="1">
+        <v>41972</v>
+      </c>
+      <c r="C11" s="1">
+        <v>42064</v>
+      </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
     </row>
@@ -575,8 +599,12 @@
       <c r="A12" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
+      <c r="B12" s="1">
+        <v>41973</v>
+      </c>
+      <c r="C12" s="1">
+        <v>42072</v>
+      </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
     </row>
@@ -584,8 +612,12 @@
       <c r="A13" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
+      <c r="B13" s="1">
+        <v>41973</v>
+      </c>
+      <c r="C13" s="1">
+        <v>42070</v>
+      </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
     </row>
@@ -593,8 +625,12 @@
       <c r="A14" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
+      <c r="B14" s="1">
+        <v>42001</v>
+      </c>
+      <c r="C14" s="1">
+        <v>42029</v>
+      </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
     </row>
@@ -602,8 +638,12 @@
       <c r="A15" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
+      <c r="B15" s="1">
+        <v>41995</v>
+      </c>
+      <c r="C15" s="1">
+        <v>42049</v>
+      </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
     </row>
@@ -611,8 +651,12 @@
       <c r="A16" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
+      <c r="B16" s="1">
+        <v>41973</v>
+      </c>
+      <c r="C16" s="1">
+        <v>42070</v>
+      </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
     </row>
@@ -620,8 +664,12 @@
       <c r="A17" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
+      <c r="B17" s="1">
+        <v>41973</v>
+      </c>
+      <c r="C17" s="1">
+        <v>42091</v>
+      </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
     </row>
@@ -629,8 +677,12 @@
       <c r="A18" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
+      <c r="B18" s="1">
+        <v>42382</v>
+      </c>
+      <c r="C18" s="1">
+        <v>42394</v>
+      </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
     </row>
@@ -638,8 +690,12 @@
       <c r="A19" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
+      <c r="B19" s="1">
+        <v>42702</v>
+      </c>
+      <c r="C19" s="1">
+        <v>42763</v>
+      </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
